--- a/gsp-compliance/BSL-Production_Technology_Inventory.xlsx
+++ b/gsp-compliance/BSL-Production_Technology_Inventory.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neeraj/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neeraj/space/Code/blowbits-docs/gsp-compliance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A17705A-8457-AE4E-A472-45A7C5697D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C272BB4-1EDE-2B4A-AE2B-4E23D3190162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29920" windowHeight="17620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Production Technology Inventory" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="45">
   <si>
     <t>Category</t>
   </si>
@@ -61,18 +61,9 @@
     <t>Debian Linux</t>
   </si>
   <si>
-    <t>12.x</t>
-  </si>
-  <si>
     <t>Container Platform</t>
   </si>
   <si>
-    <t>Docker Engine</t>
-  </si>
-  <si>
-    <t>28.x</t>
-  </si>
-  <si>
     <t>Container Operating System</t>
   </si>
   <si>
@@ -88,9 +79,6 @@
     <t>Nginx</t>
   </si>
   <si>
-    <t>1.28.x</t>
-  </si>
-  <si>
     <t>Serves static web content</t>
   </si>
   <si>
@@ -100,54 +88,36 @@
     <t>HAProxy</t>
   </si>
   <si>
-    <t>3.x</t>
-  </si>
-  <si>
     <t>Firewall</t>
   </si>
   <si>
     <t>OPNsense</t>
   </si>
   <si>
-    <t>25.x</t>
-  </si>
-  <si>
     <t>Runtime</t>
   </si>
   <si>
     <t>.NET</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>Frontend Framework</t>
   </si>
   <si>
     <t>React</t>
   </si>
   <si>
-    <t>19.x</t>
-  </si>
-  <si>
     <t>Database</t>
   </si>
   <si>
     <t>PostgreSQL</t>
   </si>
   <si>
-    <t>16.x</t>
-  </si>
-  <si>
     <t>Cache</t>
   </si>
   <si>
     <t>Redis</t>
   </si>
   <si>
-    <t>7.x</t>
-  </si>
-  <si>
     <t>Serverless</t>
   </si>
   <si>
@@ -182,6 +152,9 @@
   </si>
   <si>
     <t>AWS ACM / Let’s Encrypt</t>
+  </si>
+  <si>
+    <t>Podman</t>
   </si>
 </sst>
 </file>
@@ -223,9 +196,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,7 +512,7 @@
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
@@ -546,7 +525,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -566,7 +545,7 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
@@ -583,8 +562,8 @@
       <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
+      <c r="C3" s="2">
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -595,13 +574,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
+        <v>44</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4.3</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -612,13 +591,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -629,13 +608,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1.3</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
@@ -644,18 +623,18 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
+        <v>21</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2.6</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -666,13 +645,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="C8" s="2">
+        <v>25.1</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -683,13 +662,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
+        <v>25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>10</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -700,13 +679,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="2">
+        <v>19</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
@@ -717,13 +696,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="C11" s="2">
+        <v>18.3</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
@@ -734,13 +713,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
+        <v>31</v>
+      </c>
+      <c r="C12" s="2">
+        <v>7</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
@@ -751,12 +730,12 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D13" t="s">
@@ -768,12 +747,12 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D14" t="s">
@@ -785,12 +764,12 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2">
         <v>13</v>
       </c>
       <c r="D15" t="s">
@@ -802,13 +781,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
+        <v>39</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2.5299999999999998</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
@@ -819,36 +798,36 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>26</v>
+        <v>41</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3.7</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
